--- a/staff_forms/023_daily_shift_pass_on_form--staff_forms.xlsx
+++ b/staff_forms/023_daily_shift_pass_on_form--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shift_start_time</t>
+          <t>shift_start_time_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>shift start time</t>
+          <t>Shift Start Time 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>replacement_shift_staff_name</t>
+          <t>replacement_shift_staff_name_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>replacement shift staff name</t>
+          <t>Replacement Shift Staff Name 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>replacement_staff</t>
+          <t>replacement_staff_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>replacement staff</t>
+          <t>Replacement Staff 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>replacement_shift</t>
+          <t>replacement_shift_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>replacement shift</t>
+          <t>Replacement Shift 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>next_shift</t>
+          <t>next_shift_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>next shift</t>
+          <t>Next Shift 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -1483,24 +1483,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>replacement_staff_choices</t>
+          <t>replacement_staff_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>replacement_staff_choices</t>
+          <t>replacement_staff_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>replacement_staff_choices</t>
+          <t>replacement_staff_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,24 +1534,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>replacement_shift_choices</t>
+          <t>replacement_shift_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>replacement_shift_choices</t>
+          <t>replacement_shift_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>replacement_shift_choices</t>
+          <t>replacement_shift_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,24 +1585,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>next_shift_choices</t>
+          <t>next_shift_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'name':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'name': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>next_shift_choices</t>
+          <t>next_shift_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>next_shift_choices</t>
+          <t>next_shift_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'name':_'shift_leader'}</t>
+          <t>shift_leader</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'name': 'shift leader'}</t>
+          <t>shift leader</t>
         </is>
       </c>
     </row>
